--- a/Filtered_V3.0/COCQR_HCA_Florida_Raulerson_Hospital.xlsx
+++ b/Filtered_V3.0/COCQR_HCA_Florida_Raulerson_Hospital.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">* (*** DO NOT REMOVE ***)-ITS HM Results </t>
+          <t>* (*** DO NOT REMOVE ***)-ITSHMRO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Abstracting </t>
+          <t>3M (360 Encompass)-ABSDPI</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Admissions </t>
+          <t>3M (360 Encompass)-ADMO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Charges </t>
+          <t>3M (360 Encompass)-ITSDIRO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -971,22 +971,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS DI Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-LABRES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Lab Results (Discrete) </t>
+          <t>3M (360 Encompass)-OMORDO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-OM Orders </t>
+          <t>3M (360 Encompass)-Patient Accounting</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1381,22 +1381,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople ED Patient Visit Data</t>
+          <t>3M (360 Encompass)-iPeople EDM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Medication Administration</t>
+          <t>3M (360 Encompass)-iPeople Meds</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Nursing Assessment Forms</t>
+          <t>3M (360 Encompass)-iPeople PCS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-Admissions </t>
+          <t>AQuity Solutions (DocEP)-ADMO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-ITS HM Results </t>
+          <t>AQuity Solutions (DocEP)-ITSHMRO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alere (MAS RALS-Plus)-</t>
+          <t>Alere (MAS RALS-Plus)-ADMO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1997,7 +1997,22 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -2019,7 +2034,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alere (MAS RALS-Plus)-Admissions </t>
+          <t>Alere (MAS RALS-Plus)-labpoc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2064,22 +2079,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Admissions </t>
+          <t>BD (Pyxis Medstation ES)-ADMO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Inventory </t>
+          <t>BD (Pyxis Medstation ES)-PHAINV</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Orders </t>
+          <t>BD (Pyxis Medstation ES)-PHAORD</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Candescent Health/Envision Healthcare (Candescent Health)-</t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-ITSDIRO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2516,7 +2516,22 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -2538,7 +2553,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candescent Health/Envision Healthcare (Candescent Health)-ITS DI Results </t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-ITSDIRO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2583,7 +2598,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2620,7 +2635,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candescent Health/Envision Healthcare (Candescent Health)-ITS DI Results </t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-radord</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2666,21 +2681,6 @@
       <c r="P29" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-Admissions </t>
+          <t>Computrition (Computrition)-ADMO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-OM Orders </t>
+          <t>Computrition (Computrition)-OMORDO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion Voice)-Admissions </t>
+          <t>Dolbey (Fusion Voice)-ADMO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dolbey (Fusion)-</t>
+          <t>Dolbey (Fusion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3308,7 +3308,22 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3330,7 +3345,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion)-ITS DI Results </t>
+          <t>Dolbey (Fusion)-radord</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3375,22 +3390,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Admissions </t>
+          <t>Envision Healthcare (Envision Healthcare)-ADMO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS DI Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-CWSO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3606,17 +3606,17 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSDIRO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Scheduling </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3847,22 +3847,22 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Envision Healthcare (Envision Healthcare)-iPeople ED Patient Visit Data</t>
+          <t>Envision Healthcare (Envision Healthcare)-iPeople EDM</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florida HIE (Event Notification Service)-Admissions </t>
+          <t>Florida HIE (Event Notification Service)-ADMO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Admissions </t>
+          <t>GE (CMI - Carescape Gateway)-ADMO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>GE (Centricity - CCG PACS)-</t>
+          <t>GE (Centricity - CCG PACS)-ADMO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4362,6 +4362,21 @@
       <c r="P52" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -4383,7 +4398,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Admissions </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIRO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4433,17 +4448,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -4465,7 +4480,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-ITS DI Results </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4510,22 +4525,22 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSDIUI</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Radiology Image Status </t>
         </is>
       </c>
     </row>
@@ -4547,7 +4562,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4629,7 +4644,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-radord</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4674,22 +4689,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>ITSDIUI</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Radiology Image Status </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-</t>
+          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Admissions </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ADMO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-OM Orders </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-OMORDO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Admissions </t>
+          <t>GE (Centricity MUSE)-ADMO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Charges </t>
+          <t>GE (Centricity MUSE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5630,17 +5630,17 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-ITS HM Results </t>
+          <t>GE (Centricity MUSE)-OMORDO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5707,22 +5707,22 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-OM Orders </t>
+          <t>GE (Centricity MUSE)-Patient Accounting</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5789,22 +5789,22 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-</t>
+          <t>Google (Healthcare Data Engine - HDE)-ADMO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6078,6 +6078,21 @@
       <c r="P75" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -6099,7 +6114,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Admissions </t>
+          <t>Google (Healthcare Data Engine - HDE)-CWSO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6149,17 +6164,17 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6196,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS DI Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-IMMUN</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6231,17 +6246,17 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6278,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS HM Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSDIRO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6313,7 +6328,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -6323,7 +6338,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -6345,7 +6360,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Lab Results (Discrete) </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6395,7 +6410,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -6405,7 +6420,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -6427,7 +6442,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-MU-Immunizations</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6477,17 +6492,17 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -6509,7 +6524,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-Pathology Results</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES2</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6591,7 +6606,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Pharmacy Orders </t>
+          <t>Google (Healthcare Data Engine - HDE)-PHAORD</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6673,7 +6688,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Scheduling </t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople EDM</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6723,17 +6738,17 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -6755,7 +6770,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople ED Patient Visit Data</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople Meds</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6805,17 +6820,17 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6852,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Medication Administration</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople PCS</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6887,17 +6902,17 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6934,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Nursing Assessment Forms</t>
+          <t>Google (Healthcare Data Engine - HDE)-radord</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6965,21 +6980,6 @@
       <c r="P86" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-ADMO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7109,6 +7109,21 @@
       <c r="P88" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -7130,7 +7145,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7176,6 +7191,21 @@
       <c r="P89" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>CWSO</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>SIU</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -7197,7 +7227,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Admissions </t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7247,17 +7277,17 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -7279,7 +7309,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-IMMUN</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7329,17 +7359,17 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7391,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7443,7 +7473,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS HM Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7493,7 +7523,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -7503,7 +7533,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -7525,7 +7555,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-ITSHMRO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7575,7 +7605,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -7585,7 +7615,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -7607,7 +7637,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7689,7 +7719,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-MU-Immunizations</t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7739,17 +7769,17 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -7771,7 +7801,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-OM Orders </t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7821,17 +7851,17 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7883,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7935,7 +7965,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-OMORDO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7985,17 +8015,17 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8047,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Pharmacy Orders </t>
+          <t>HCA (Cloudera Kafka)-PHAORD</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8099,7 +8129,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8149,17 +8179,17 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8211,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8231,17 +8261,17 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8293,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople Meds</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8313,17 +8343,17 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -8345,7 +8375,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8395,17 +8425,17 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8427,7 +8457,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Medication Administration</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8477,17 +8507,17 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8539,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8555,21 +8585,6 @@
       <c r="P106" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8606,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8637,21 +8652,6 @@
       <c r="P107" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (EDW CDM)-Scheduling </t>
+          <t>HCA (EDW CDM)-CWSO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>HCA (HealthTrust:IBM Integration Bus-IIB)-</t>
+          <t>HCA (HealthTrust:IBM Integration Bus-IIB)-mmitem</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Revive)-ITS HM Results </t>
+          <t>HCA (Revive)-ITSHMRO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>HCA (SMART to Optiflex)-</t>
+          <t>HCA (SMART to Optiflex)-multi</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-ADMO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9326,7 +9326,22 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9348,7 +9363,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (SMART)-Admissions </t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9393,22 +9408,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R118" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -9492,7 +9492,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ADMO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9538,6 +9538,21 @@
       <c r="P120" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9559,7 +9574,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Admissions </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9609,17 +9624,17 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9656,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS DI Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9691,17 +9706,17 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -9723,7 +9738,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS HM Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-IMMUN</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9773,17 +9788,17 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -9805,7 +9820,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSDIRO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9855,7 +9870,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -9865,7 +9880,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -9887,7 +9902,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Electronic Lab Reporting</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSHMRO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9937,7 +9952,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>PHELR</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -9947,7 +9962,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>MU-Electronic Lab Reporting</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -9969,7 +9984,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -10019,17 +10034,17 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -10051,7 +10066,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES2</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -10101,17 +10116,17 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10148,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -10215,7 +10230,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -10297,7 +10312,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-Pathology Results</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHAORD</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10347,17 +10362,17 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -10379,7 +10394,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHELR</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -10429,17 +10444,17 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>PHELR</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>MU-Electronic Lab Reporting</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10476,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHSS</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -10511,17 +10526,17 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -10543,7 +10558,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople EDM</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10593,17 +10608,17 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10640,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Meds</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10675,17 +10690,17 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10722,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople PCS</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10757,17 +10772,17 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -10789,7 +10804,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-radord</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10835,21 +10850,6 @@
       <c r="P136" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-</t>
+          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Null-Terminates Message)-</t>
+          <t>HCA D&amp;IS (Null-Terminates Message)-iti08</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-</t>
+          <t>HCA D&amp;IS (Waterpark)-ADMO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -11463,6 +11463,21 @@
       <c r="P145" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -11484,7 +11499,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Admissions </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11534,17 +11549,17 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -11566,7 +11581,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS DI Results </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11616,17 +11631,17 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -11648,7 +11663,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS HM Results </t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUN</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11698,17 +11713,17 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -11730,7 +11745,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Immunization Query</t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUNQRY</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11812,7 +11827,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (Waterpark)-ITSDIRO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11862,7 +11877,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -11872,7 +11887,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -11894,7 +11909,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (Waterpark)-ITSHMRO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11944,17 +11959,17 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -11976,7 +11991,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -12026,17 +12041,17 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -12058,7 +12073,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES2</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -12108,17 +12123,17 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -12140,7 +12155,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -12195,12 +12210,12 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12237,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Pathology Results</t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -12272,17 +12287,17 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -12304,7 +12319,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-PHAORD</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -12386,7 +12401,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-PHSS</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12436,17 +12451,17 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12483,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople EDM</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12518,17 +12533,17 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -12550,7 +12565,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople Meds</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -12600,17 +12615,17 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -12632,7 +12647,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople PCS</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12682,17 +12697,17 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (Waterpark)-radord</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12760,21 +12775,6 @@
       <c r="P161" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R161" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (Charge Master)-SMART Procedure Codes </t>
+          <t>HCA Parallon (Charge Master)-MISPROC</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (eCapture)-Admissions </t>
+          <t>HCA Parallon (eCapture)-ADMO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Admissions </t>
+          <t>Health Catalyst (HCare Hub)-ADMO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -13228,7 +13228,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS DI Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSDIRO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS HM Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSHMRO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Lab Results (Discrete) </t>
+          <t>Health Catalyst (HCare Hub)-LABRES</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Health Catalyst (HCare Hub)-Pathology Results</t>
+          <t>Health Catalyst (HCare Hub)-LABRES2</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Admissions </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-ADMO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Clinical Monitoring Results </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-PCSCMI</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13844,7 +13844,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Admissions </t>
+          <t>Hospira (Theradoc)-ADMO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS DI Results </t>
+          <t>Hospira (Theradoc)-ITSDIRO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS HM Results </t>
+          <t>Hospira (Theradoc)-ITSHMRO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Lab Results (Discrete) </t>
+          <t>Hospira (Theradoc)-LABRES</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-OM Orders </t>
+          <t>Hospira (Theradoc)-OMORDO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Pharmacy Orders </t>
+          <t>Hospira (Theradoc)-PHAORD</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople ED Patient Visit Data</t>
+          <t>Hospira (Theradoc)-iPeople EDM</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Medication Administration</t>
+          <t>Hospira (Theradoc)-iPeople Meds</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Nursing Assessment Forms</t>
+          <t>Hospira (Theradoc)-iPeople PCS</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase RX-ADT/Link Orders)-Admissions </t>
+          <t>Hyland (Onbase RX-ADT/Link Orders)-ADMO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase)-Admissions </t>
+          <t>Hyland (Onbase)-ADMO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM (Consent Management)-Admissions </t>
+          <t>IBM (Consent Management)-ADMO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-</t>
+          <t>Iodine Software (Iodine-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -15477,6 +15477,21 @@
       <c r="P197" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -15498,7 +15513,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Admissions </t>
+          <t>Iodine Software (Iodine-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -15548,17 +15563,17 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -15580,7 +15595,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS DI Results </t>
+          <t>Iodine Software (Iodine-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -15630,7 +15645,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
@@ -15640,7 +15655,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -15662,7 +15677,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS HM Results </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -15712,7 +15727,7 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -15722,7 +15737,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -15744,7 +15759,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Lab Results (Discrete) </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES2</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -15794,7 +15809,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
@@ -15804,7 +15819,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -15826,7 +15841,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-OM Orders </t>
+          <t>Iodine Software (Iodine-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -15908,7 +15923,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-Pathology Results</t>
+          <t>Iodine Software (Iodine-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -15958,17 +15973,17 @@
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -15990,7 +16005,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Pharmacy Orders </t>
+          <t>Iodine Software (Iodine-Facility)-iPeople EDM</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -16040,17 +16055,17 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -16072,7 +16087,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople ED Patient Visit Data</t>
+          <t>Iodine Software (Iodine-Facility)-iPeople Meds</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -16122,17 +16137,17 @@
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -16154,7 +16169,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople Medication Administration</t>
+          <t>Iodine Software (Iodine-Facility)-iPeople PCS</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -16204,17 +16219,17 @@
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -16236,7 +16251,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople Nursing Assessment Forms</t>
+          <t>Iodine Software (Iodine-Facility)-radord</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -16282,21 +16297,6 @@
       <c r="P207" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R207" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">LabCorp (LabCorp)-Ref Lab Orders </t>
+          <t>LabCorp (LabCorp)-LABRR</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -16425,22 +16425,22 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>LABSO</t>
+          <t>LABRR</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ref Lab Orders </t>
+          <t>Ref Lab Results</t>
         </is>
       </c>
     </row>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>LabCorp (LabCorp)-Ref Lab Results</t>
+          <t>LabCorp (LabCorp)-LABSO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -16507,22 +16507,22 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>LABRR</t>
+          <t>LABSO</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>Ref Lab Results</t>
+          <t xml:space="preserve">Ref Lab Orders </t>
         </is>
       </c>
     </row>
@@ -16606,7 +16606,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>McKesson (MPF-Patient Folder/HPF Facility to ED Billing)-</t>
+          <t>McKesson (MPF-Patient Folder/HPF Facility to ED Billing)-bill</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">McKesson (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>McKesson (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -16879,7 +16879,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Admissions </t>
+          <t>Medaxion (Medaxion Pulse)-ADMO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Scheduling </t>
+          <t>Medaxion (Medaxion Pulse)-CWSO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-</t>
+          <t>Meditech (HCA 5.6)-ADMO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -17295,6 +17295,21 @@
       <c r="P221" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -17316,7 +17331,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Admissions </t>
+          <t>Meditech (HCA 5.6)-ITSDIRO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -17366,17 +17381,17 @@
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -17398,7 +17413,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS DI Results </t>
+          <t>Meditech (HCA 5.6)-ITSHMRO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -17448,7 +17463,7 @@
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
@@ -17458,7 +17473,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -17480,7 +17495,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS HM Results </t>
+          <t>Meditech (HCA 5.6)-LABRES</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -17530,7 +17545,7 @@
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
@@ -17540,7 +17555,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -17562,7 +17577,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Lab Results (Discrete) </t>
+          <t>Meditech (HCA 5.6)-LABRES2</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -17612,7 +17627,7 @@
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
@@ -17622,7 +17637,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -17644,7 +17659,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-OM Orders </t>
+          <t>Meditech (HCA 5.6)-OMORDO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -17726,7 +17741,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-Pathology Results</t>
+          <t>Meditech (HCA 5.6)-PHAORD</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -17776,17 +17791,17 @@
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -17808,7 +17823,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Pharmacy Orders </t>
+          <t>Meditech (HCA 5.6)-radord</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -17854,21 +17869,6 @@
       <c r="P228" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q228" t="inlineStr">
-        <is>
-          <t>PHAORD</t>
-        </is>
-      </c>
-      <c r="R228" t="inlineStr">
-        <is>
-          <t>RDE</t>
-        </is>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -17952,7 +17952,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Admissions </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ADMO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -18198,7 +18198,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -18280,7 +18280,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -18588,7 +18588,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS DI Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -18896,7 +18896,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Admissions </t>
+          <t>Mobile Heartbeat (imobile)-ADMO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Lab Results (Discrete) </t>
+          <t>Mobile Heartbeat (imobile)-LABRES</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -19122,7 +19122,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Omnicell (Optiflex to SMART)-</t>
+          <t>Omnicell (Optiflex to SMART)-mmrepl</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Admissions </t>
+          <t>Omnicell (Optiflex)-ADMO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -19333,7 +19333,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Charges </t>
+          <t>Omnicell (Optiflex)-Patient Accounting</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -19477,7 +19477,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport Health Communications, Inc. (eCare Next)-Admissions </t>
+          <t>Passport Health Communications, Inc. (eCare Next)-ADMO</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -19621,7 +19621,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Patient Keeper (Portal)-</t>
+          <t>Patient Keeper (Portal)-ITSHMRO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -19667,6 +19667,21 @@
       <c r="P252" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>ITSHMRO</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -19688,7 +19703,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient Keeper (Portal)-ITS HM Results </t>
+          <t>Patient Keeper (Portal)-eps</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -19734,21 +19749,6 @@
       <c r="P253" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q253" t="inlineStr">
-        <is>
-          <t>ITSHMRO</t>
-        </is>
-      </c>
-      <c r="R253" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rauland (Responder)-Admissions </t>
+          <t>Rauland (Responder)-ADMO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -19976,7 +19976,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Siemens (RapidComm)-Admissions </t>
+          <t>Siemens (RapidComm)-ADMO</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -20120,7 +20120,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-Admissions </t>
+          <t>TeleSpecialists (TeleCare)-ADMO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-ITS HM Results </t>
+          <t>TeleSpecialists (TeleCare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -20284,7 +20284,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-OM Orders </t>
+          <t>TeleSpecialists (TeleCare)-OMORDO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-Admissions </t>
+          <t>TeleTracking (TransferCenter IQ)-ADMO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-OM Orders </t>
+          <t>TeleTracking (TransferCenter IQ)-OMORDO</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -20592,7 +20592,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>TeleTracking (TransferCenter IQ)-iPeople Nursing Assessment Forms</t>
+          <t>TeleTracking (TransferCenter IQ)-iPeople PCS</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -20736,7 +20736,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Ventana Medical Systems (VANTAGE)-</t>
+          <t>Ventana Medical Systems (VANTAGE)-pthord</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -20865,7 +20865,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Admissions </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -20947,7 +20947,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITS DI Results </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -21029,7 +21029,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Lab Results (Discrete) </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -21275,7 +21275,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Pharmacy Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -21357,7 +21357,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople ED Patient Visit Data</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople EDM</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -21439,7 +21439,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Medication Administration</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Meds</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -21583,7 +21583,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Volpara Health (Aspen Breast)-</t>
+          <t>Volpara Health (Aspen Breast)-radord</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -21712,7 +21712,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-</t>
+          <t>dbMotion (db Motion)-ADMO</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -21758,6 +21758,21 @@
       <c r="P280" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -21779,7 +21794,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Admissions </t>
+          <t>dbMotion (db Motion)-IMMUN</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -21829,17 +21844,17 @@
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -21861,7 +21876,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS DI Results </t>
+          <t>dbMotion (db Motion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -21943,7 +21958,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS HM Results </t>
+          <t>dbMotion (db Motion)-ITSHMRO</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -22025,7 +22040,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Lab Results (Discrete) </t>
+          <t>dbMotion (db Motion)-LABRES</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -22107,7 +22122,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-MU-Immunizations</t>
+          <t>dbMotion (db Motion)-LABRES2</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -22157,17 +22172,17 @@
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -22189,7 +22204,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-Pathology Results</t>
+          <t>dbMotion (db Motion)-PHAORD</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -22239,17 +22254,17 @@
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -22271,7 +22286,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Pharmacy Orders </t>
+          <t>dbMotion (db Motion)-iPeople EDM</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -22321,17 +22336,17 @@
       </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -22353,7 +22368,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople ED Patient Visit Data</t>
+          <t>dbMotion (db Motion)-iPeople PCS</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -22403,17 +22418,17 @@
       </c>
       <c r="Q288" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -22435,7 +22450,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople Nursing Assessment Forms</t>
+          <t>dbMotion (db Motion)-radord</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -22481,21 +22496,6 @@
       <c r="P289" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q289" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R289" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S289" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -22579,7 +22579,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (HCA 5.6)-iPeople EDM</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -22661,7 +22661,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople Medication Administration</t>
+          <t>iPeople (HCA 5.6)-iPeople Meds</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -22805,7 +22805,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">iPeople (iPeople MT56)-OM Orders </t>
+          <t>iPeople (iPeople MT56)-OMORDO</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -22887,7 +22887,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (iPeople MT56)-iPeople EDM</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -22969,7 +22969,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Medication Administration</t>
+          <t>iPeople (iPeople MT56)-iPeople Meds</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -23051,7 +23051,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Nursing Assessment Forms</t>
+          <t>iPeople (iPeople MT56)-iPeople PCS</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
